--- a/backend/data/financials_by_company/0GA.F.xlsx
+++ b/backend/data/financials_by_company/0GA.F.xlsx
@@ -677,562 +677,562 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.070892</v>
+        <v>0.079695</v>
       </c>
       <c r="D2" t="n">
-        <v>-3952444</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>-3481285</v>
+      </c>
+      <c r="E2" t="n">
+        <v>900</v>
+      </c>
+      <c r="F2" t="n">
+        <v>900</v>
+      </c>
       <c r="G2" t="n">
-        <v>-4487054</v>
+        <v>-3404436</v>
       </c>
       <c r="H2" t="n">
-        <v>-75298</v>
+        <v>29198</v>
       </c>
       <c r="I2" t="n">
-        <v>13819</v>
+        <v>49309</v>
       </c>
       <c r="J2" t="n">
-        <v>-3952444</v>
+        <v>-3481285</v>
       </c>
       <c r="K2" t="n">
-        <v>-3971010</v>
+        <v>-3510483</v>
       </c>
       <c r="L2" t="n">
-        <v>-842812</v>
+        <v>-188766</v>
       </c>
       <c r="M2" t="n">
-        <v>858410</v>
-      </c>
-      <c r="N2" t="n">
-        <v>36116</v>
-      </c>
+        <v>188766</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-4487054</v>
+        <v>-3404436</v>
       </c>
       <c r="P2" t="n">
-        <v>-4487054</v>
+        <v>-3404436</v>
       </c>
       <c r="Q2" t="n">
-        <v>4604666</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>3653060</v>
+      </c>
+      <c r="R2" t="n">
+        <v>165703</v>
+      </c>
       <c r="S2" t="n">
-        <v>-3986608</v>
+        <v>-3510390</v>
       </c>
       <c r="T2" t="n">
-        <v>3762505</v>
+        <v>3645723</v>
       </c>
       <c r="U2" t="n">
-        <v>3762505</v>
+        <v>3645723</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>-0.93357</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>-0.93357</v>
       </c>
       <c r="X2" t="n">
-        <v>198627492</v>
+        <v>-3403536</v>
       </c>
       <c r="Y2" t="n">
-        <v>198627492</v>
+        <v>-3403536</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>198627492</v>
+        <v>-3403536</v>
       </c>
       <c r="AB2" t="n">
-        <v>198627492</v>
+        <v>-3403536</v>
       </c>
       <c r="AC2" t="n">
-        <v>203114546</v>
+        <v>900</v>
       </c>
       <c r="AD2" t="n">
-        <v>-4487054</v>
+        <v>-3404436</v>
       </c>
       <c r="AE2" t="n">
-        <v>-342366</v>
+        <v>-294813</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4829420</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+        <v>-3699249</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-900</v>
+      </c>
       <c r="AI2" t="n">
-        <v>-842812</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20518</v>
-      </c>
+        <v>-188766</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>858410</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36116</v>
-      </c>
+        <v>188766</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-3986608</v>
+        <v>-3510391</v>
       </c>
       <c r="AN2" t="n">
-        <v>4590847</v>
+        <v>3603751</v>
       </c>
       <c r="AO2" t="n">
-        <v>2196090</v>
+        <v>1743340</v>
       </c>
       <c r="AP2" t="n">
-        <v>18566</v>
+        <v>29198</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18566</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>29198</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1173315</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>239767</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>933548</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>165703</v>
+      </c>
       <c r="AV2" t="n">
-        <v>604239</v>
+        <v>93360</v>
       </c>
       <c r="AW2" t="n">
-        <v>13819</v>
+        <v>49309</v>
       </c>
       <c r="AX2" t="n">
-        <v>618058</v>
+        <v>142669</v>
       </c>
       <c r="AY2" t="n">
-        <v>618058</v>
+        <v>142669</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.052135</v>
+        <v>0.067194</v>
       </c>
       <c r="D3" t="n">
-        <v>-3815931</v>
+        <v>-3478947</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-4218923</v>
+        <v>-3555447</v>
       </c>
       <c r="H3" t="n">
-        <v>12687</v>
+        <v>31926</v>
       </c>
       <c r="I3" t="n">
-        <v>10909</v>
+        <v>36216</v>
       </c>
       <c r="J3" t="n">
-        <v>-3815931</v>
+        <v>-3478947</v>
       </c>
       <c r="K3" t="n">
-        <v>-3834081</v>
+        <v>-3510873</v>
       </c>
       <c r="L3" t="n">
-        <v>-611122</v>
+        <v>-313524</v>
       </c>
       <c r="M3" t="n">
-        <v>616895</v>
+        <v>300686</v>
       </c>
       <c r="N3" t="n">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="O3" t="n">
-        <v>-4218923</v>
+        <v>-3555447</v>
       </c>
       <c r="P3" t="n">
-        <v>-4218923</v>
+        <v>-3555447</v>
       </c>
       <c r="Q3" t="n">
-        <v>4157733</v>
+        <v>3786558</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-3839900</v>
+        <v>-3497874</v>
       </c>
       <c r="T3" t="n">
-        <v>3698843</v>
+        <v>3720277</v>
       </c>
       <c r="U3" t="n">
-        <v>3698843</v>
+        <v>3720277</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.14</v>
+        <v>-1</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.14</v>
+        <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-4216681</v>
+        <v>-3645758</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4216681</v>
+        <v>-3645758</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4216681</v>
+        <v>-3645758</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4216681</v>
+        <v>-3645758</v>
       </c>
       <c r="AC3" t="n">
-        <v>2242</v>
+        <v>-90311</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4218923</v>
+        <v>-3555447</v>
       </c>
       <c r="AE3" t="n">
-        <v>-232053</v>
+        <v>-256112</v>
       </c>
       <c r="AF3" t="n">
-        <v>-4450976</v>
+        <v>-3811559</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-611122</v>
+        <v>-313524</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5463</v>
+        <v>12838</v>
       </c>
       <c r="AK3" t="n">
-        <v>616895</v>
+        <v>300686</v>
       </c>
       <c r="AL3" t="n">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3839900</v>
+        <v>-3497875</v>
       </c>
       <c r="AN3" t="n">
-        <v>4146824</v>
+        <v>3750342</v>
       </c>
       <c r="AO3" t="n">
-        <v>2085620</v>
+        <v>1881779</v>
       </c>
       <c r="AP3" t="n">
-        <v>18150</v>
+        <v>19089</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18150</v>
+        <v>19089</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>306924</v>
+        <v>252467</v>
       </c>
       <c r="AW3" t="n">
-        <v>10909</v>
+        <v>36216</v>
       </c>
       <c r="AX3" t="n">
-        <v>317833</v>
+        <v>288683</v>
       </c>
       <c r="AY3" t="n">
-        <v>317833</v>
+        <v>288683</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.067194</v>
+        <v>0.052135</v>
       </c>
       <c r="D4" t="n">
-        <v>-3478947</v>
+        <v>-3815931</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-3555447</v>
+        <v>-4218923</v>
       </c>
       <c r="H4" t="n">
-        <v>31926</v>
+        <v>12687</v>
       </c>
       <c r="I4" t="n">
-        <v>36216</v>
+        <v>10909</v>
       </c>
       <c r="J4" t="n">
-        <v>-3478947</v>
+        <v>-3815931</v>
       </c>
       <c r="K4" t="n">
-        <v>-3510873</v>
+        <v>-3834081</v>
       </c>
       <c r="L4" t="n">
-        <v>-313524</v>
+        <v>-611122</v>
       </c>
       <c r="M4" t="n">
-        <v>300686</v>
+        <v>616895</v>
       </c>
       <c r="N4" t="n">
-        <v>68</v>
+        <v>310</v>
       </c>
       <c r="O4" t="n">
-        <v>-3555447</v>
+        <v>-4218923</v>
       </c>
       <c r="P4" t="n">
-        <v>-3555447</v>
+        <v>-4218923</v>
       </c>
       <c r="Q4" t="n">
-        <v>3786558</v>
+        <v>4157733</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-3497874</v>
+        <v>-3839900</v>
       </c>
       <c r="T4" t="n">
-        <v>3720277</v>
+        <v>3698843</v>
       </c>
       <c r="U4" t="n">
-        <v>3720277</v>
+        <v>3698843</v>
       </c>
       <c r="V4" t="n">
-        <v>-1</v>
+        <v>-1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>-1</v>
+        <v>-1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>-3645758</v>
+        <v>-4216681</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3645758</v>
+        <v>-4216681</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3645758</v>
+        <v>-4216681</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3645758</v>
+        <v>-4216681</v>
       </c>
       <c r="AC4" t="n">
-        <v>-90311</v>
+        <v>2242</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3555447</v>
+        <v>-4218923</v>
       </c>
       <c r="AE4" t="n">
-        <v>-256112</v>
+        <v>-232053</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3811559</v>
+        <v>-4450976</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-313524</v>
+        <v>-611122</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12838</v>
+        <v>-5463</v>
       </c>
       <c r="AK4" t="n">
-        <v>300686</v>
+        <v>616895</v>
       </c>
       <c r="AL4" t="n">
-        <v>68</v>
+        <v>310</v>
       </c>
       <c r="AM4" t="n">
-        <v>-3497875</v>
+        <v>-3839900</v>
       </c>
       <c r="AN4" t="n">
-        <v>3750342</v>
+        <v>4146824</v>
       </c>
       <c r="AO4" t="n">
-        <v>1881779</v>
+        <v>2085620</v>
       </c>
       <c r="AP4" t="n">
-        <v>19089</v>
+        <v>18150</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19089</v>
+        <v>18150</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>252467</v>
+        <v>306924</v>
       </c>
       <c r="AW4" t="n">
-        <v>36216</v>
+        <v>10909</v>
       </c>
       <c r="AX4" t="n">
-        <v>288683</v>
+        <v>317833</v>
       </c>
       <c r="AY4" t="n">
-        <v>288683</v>
+        <v>317833</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.079695</v>
+        <v>0.070892</v>
       </c>
       <c r="D5" t="n">
-        <v>-3481285</v>
-      </c>
-      <c r="E5" t="n">
-        <v>900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>900</v>
-      </c>
+        <v>-3952444</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-3404436</v>
+        <v>-4487054</v>
       </c>
       <c r="H5" t="n">
-        <v>29198</v>
+        <v>-75298</v>
       </c>
       <c r="I5" t="n">
-        <v>49309</v>
+        <v>13819</v>
       </c>
       <c r="J5" t="n">
-        <v>-3481285</v>
+        <v>-3952444</v>
       </c>
       <c r="K5" t="n">
-        <v>-3510483</v>
+        <v>-3971010</v>
       </c>
       <c r="L5" t="n">
-        <v>-188766</v>
+        <v>-842812</v>
       </c>
       <c r="M5" t="n">
-        <v>188766</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>858410</v>
+      </c>
+      <c r="N5" t="n">
+        <v>36116</v>
+      </c>
       <c r="O5" t="n">
-        <v>-3404436</v>
+        <v>-4487054</v>
       </c>
       <c r="P5" t="n">
-        <v>-3404436</v>
+        <v>-4487054</v>
       </c>
       <c r="Q5" t="n">
-        <v>3653060</v>
-      </c>
-      <c r="R5" t="n">
-        <v>165703</v>
-      </c>
+        <v>4604666</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-3510390</v>
+        <v>-3986608</v>
       </c>
       <c r="T5" t="n">
-        <v>3645723</v>
+        <v>3762505</v>
       </c>
       <c r="U5" t="n">
-        <v>3645723</v>
+        <v>3762505</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.93357</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.93357</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-3403536</v>
+        <v>198627492</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3403536</v>
+        <v>198627492</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3403536</v>
+        <v>198627492</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3403536</v>
+        <v>198627492</v>
       </c>
       <c r="AC5" t="n">
-        <v>900</v>
+        <v>203114546</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3404436</v>
+        <v>-4487054</v>
       </c>
       <c r="AE5" t="n">
-        <v>-294813</v>
+        <v>-342366</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3699249</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-900</v>
-      </c>
+        <v>-4829420</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-188766</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-842812</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20518</v>
+      </c>
       <c r="AK5" t="n">
-        <v>188766</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>858410</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>36116</v>
+      </c>
       <c r="AM5" t="n">
-        <v>-3510391</v>
+        <v>-3986608</v>
       </c>
       <c r="AN5" t="n">
-        <v>3603751</v>
+        <v>4590847</v>
       </c>
       <c r="AO5" t="n">
-        <v>1743340</v>
+        <v>2196090</v>
       </c>
       <c r="AP5" t="n">
-        <v>29198</v>
+        <v>18566</v>
       </c>
       <c r="AQ5" t="n">
-        <v>29198</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1173315</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>239767</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>933548</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>165703</v>
-      </c>
+        <v>18566</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>93360</v>
+        <v>604239</v>
       </c>
       <c r="AW5" t="n">
-        <v>49309</v>
+        <v>13819</v>
       </c>
       <c r="AX5" t="n">
-        <v>142669</v>
+        <v>618058</v>
       </c>
       <c r="AY5" t="n">
-        <v>142669</v>
+        <v>618058</v>
       </c>
     </row>
   </sheetData>
@@ -1543,660 +1543,660 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>14027</v>
+        <v>14582</v>
       </c>
       <c r="C2" t="n">
-        <v>3748478</v>
+        <v>3645723</v>
       </c>
       <c r="D2" t="n">
-        <v>3762505</v>
+        <v>3660305</v>
       </c>
       <c r="E2" t="n">
-        <v>3888907</v>
+        <v>2308445</v>
       </c>
       <c r="F2" t="n">
-        <v>4947505</v>
+        <v>5130180</v>
       </c>
       <c r="G2" t="n">
-        <v>-4268114</v>
+        <v>-1565432</v>
       </c>
       <c r="H2" t="n">
-        <v>679391</v>
+        <v>3564748</v>
       </c>
       <c r="I2" t="n">
-        <v>291838</v>
+        <v>3294077</v>
       </c>
       <c r="J2" t="n">
-        <v>-4268114</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>-1565432</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
       <c r="L2" t="n">
-        <v>-4268114</v>
+        <v>-1565432</v>
       </c>
       <c r="M2" t="n">
-        <v>185688</v>
+        <v>3564748</v>
       </c>
       <c r="N2" t="n">
-        <v>-4268114</v>
+        <v>-1565432</v>
       </c>
       <c r="O2" t="n">
-        <v>-4268114</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8861088</v>
-      </c>
+        <v>-1565432</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>-4264749</v>
+        <v>-3413845</v>
       </c>
       <c r="R2" t="n">
-        <v>13311854</v>
+        <v>12734731</v>
       </c>
       <c r="S2" t="n">
-        <v>94063</v>
+        <v>91508</v>
       </c>
       <c r="T2" t="n">
-        <v>94063</v>
+        <v>91508</v>
       </c>
       <c r="U2" t="n">
-        <v>6711786</v>
+        <v>5530440</v>
       </c>
       <c r="V2" t="n">
-        <v>5018054</v>
+        <v>5130181</v>
       </c>
       <c r="W2" t="n">
-        <v>564252</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>4453802</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>5130180</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>4453802</v>
+        <v>5130180</v>
       </c>
       <c r="AA2" t="n">
-        <v>1693732</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>400259</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>20701</v>
+      </c>
       <c r="AC2" t="n">
-        <v>493703</v>
+        <v>351353</v>
       </c>
       <c r="AD2" t="n">
-        <v>493703</v>
+        <v>351353</v>
       </c>
       <c r="AE2" t="n">
-        <v>1200029</v>
+        <v>379558</v>
       </c>
       <c r="AF2" t="n">
-        <v>779877</v>
+        <v>200565</v>
       </c>
       <c r="AG2" t="n">
-        <v>420152</v>
+        <v>178993</v>
       </c>
       <c r="AH2" t="n">
-        <v>2443672</v>
+        <v>3965008</v>
       </c>
       <c r="AI2" t="n">
-        <v>458102</v>
+        <v>270672</v>
       </c>
       <c r="AJ2" t="n">
-        <v>81508</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>350497</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>350497</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+        <v>123910</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>26097</v>
+        <v>146762</v>
       </c>
       <c r="AR2" t="n">
-        <v>-62286</v>
+        <v>-200379</v>
       </c>
       <c r="AS2" t="n">
-        <v>88383</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>18660</v>
-      </c>
+        <v>347141</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>69723</v>
+        <v>347141</v>
       </c>
       <c r="AV2" t="n">
-        <v>1985570</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>3694336</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>324965</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>12073</v>
-      </c>
+        <v>58706</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>8804</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>159532</v>
+        <v>602567</v>
       </c>
       <c r="BC2" t="n">
-        <v>430402</v>
+        <v>107624</v>
       </c>
       <c r="BD2" t="n">
-        <v>1058598</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>2916634</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>94899</v>
+      </c>
       <c r="BF2" t="n">
-        <v>1058598</v>
+        <v>2821735</v>
       </c>
       <c r="BG2" t="n">
-        <v>1058598</v>
+        <v>2821735</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>17500</v>
+        <v>17750</v>
       </c>
       <c r="C3" t="n">
-        <v>3702777</v>
+        <v>3642555</v>
       </c>
       <c r="D3" t="n">
-        <v>3720277</v>
+        <v>3660305</v>
       </c>
       <c r="E3" t="n">
-        <v>4918321</v>
+        <v>3369881</v>
       </c>
       <c r="F3" t="n">
-        <v>7429212</v>
+        <v>7093085</v>
       </c>
       <c r="G3" t="n">
-        <v>-3937157</v>
+        <v>956993</v>
       </c>
       <c r="H3" t="n">
-        <v>3513290</v>
+        <v>8050078</v>
       </c>
       <c r="I3" t="n">
-        <v>2603430</v>
+        <v>3435087</v>
       </c>
       <c r="J3" t="n">
-        <v>-3937157</v>
+        <v>956993</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-3915922</v>
+        <v>956993</v>
       </c>
       <c r="M3" t="n">
-        <v>3513290</v>
+        <v>7997686</v>
       </c>
       <c r="N3" t="n">
-        <v>-3915922</v>
+        <v>956993</v>
       </c>
       <c r="O3" t="n">
-        <v>-3915922</v>
+        <v>956993</v>
       </c>
       <c r="P3" t="n">
-        <v>5168376</v>
+        <v>1755000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4224107</v>
+        <v>-13863485</v>
       </c>
       <c r="R3" t="n">
-        <v>13093064</v>
+        <v>12734731</v>
       </c>
       <c r="S3" t="n">
-        <v>93007</v>
+        <v>91508</v>
       </c>
       <c r="T3" t="n">
-        <v>93007</v>
+        <v>91508</v>
       </c>
       <c r="U3" t="n">
-        <v>8309130</v>
+        <v>8212823</v>
       </c>
       <c r="V3" t="n">
-        <v>7599017</v>
+        <v>7040693</v>
       </c>
       <c r="W3" t="n">
-        <v>169805</v>
+        <v>2040980</v>
       </c>
       <c r="X3" t="n">
-        <v>7429212</v>
+        <v>7040693</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>7429212</v>
+        <v>7040693</v>
       </c>
       <c r="AA3" t="n">
-        <v>710113</v>
+        <v>1172130</v>
       </c>
       <c r="AB3" t="n">
-        <v>249908</v>
+        <v>383327</v>
       </c>
       <c r="AC3" t="n">
-        <v>428352</v>
+        <v>52392</v>
       </c>
       <c r="AD3" t="n">
-        <v>428352</v>
+        <v>52392</v>
       </c>
       <c r="AE3" t="n">
-        <v>710113</v>
+        <v>640170</v>
       </c>
       <c r="AF3" t="n">
-        <v>373814</v>
+        <v>390463</v>
       </c>
       <c r="AG3" t="n">
-        <v>336299</v>
+        <v>249707</v>
       </c>
       <c r="AH3" t="n">
-        <v>4393208</v>
+        <v>9169816</v>
       </c>
       <c r="AI3" t="n">
-        <v>1076437</v>
+        <v>4562598</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100293</v>
+        <v>111368</v>
       </c>
       <c r="AK3" t="n">
-        <v>918218</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>918218</v>
-      </c>
+        <v>111368</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>11178</v>
       </c>
       <c r="AN3" t="n">
         <v>11178</v>
       </c>
-      <c r="AO3" t="n">
-        <v>21235</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>21235</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>36691</v>
+        <v>33643</v>
       </c>
       <c r="AR3" t="n">
-        <v>-168158</v>
+        <v>-156174</v>
       </c>
       <c r="AS3" t="n">
-        <v>204849</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>18659</v>
-      </c>
+        <v>189817</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>186190</v>
+        <v>189817</v>
       </c>
       <c r="AV3" t="n">
-        <v>3313543</v>
+        <v>4607217</v>
       </c>
       <c r="AW3" t="n">
         <v>-1</v>
       </c>
       <c r="AX3" t="n">
-        <v>64236</v>
+        <v>70646</v>
       </c>
       <c r="AY3" t="n">
-        <v>77199</v>
+        <v>1602</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>12073</v>
+        <v>583384</v>
       </c>
       <c r="BB3" t="n">
-        <v>536749</v>
+        <v>562007</v>
       </c>
       <c r="BC3" t="n">
-        <v>176631</v>
+        <v>133951</v>
       </c>
       <c r="BD3" t="n">
-        <v>2510891</v>
+        <v>3817634</v>
       </c>
       <c r="BE3" t="n">
-        <v>918218</v>
+        <v>94430</v>
       </c>
       <c r="BF3" t="n">
-        <v>2510891</v>
+        <v>3723204</v>
       </c>
       <c r="BG3" t="n">
-        <v>2510891</v>
+        <v>3723204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>17750</v>
+        <v>17500</v>
       </c>
       <c r="C4" t="n">
-        <v>3642555</v>
+        <v>3702777</v>
       </c>
       <c r="D4" t="n">
-        <v>3660305</v>
+        <v>3720277</v>
       </c>
       <c r="E4" t="n">
-        <v>3369881</v>
+        <v>4918321</v>
       </c>
       <c r="F4" t="n">
-        <v>7093085</v>
+        <v>7429212</v>
       </c>
       <c r="G4" t="n">
-        <v>956993</v>
+        <v>-3937157</v>
       </c>
       <c r="H4" t="n">
-        <v>8050078</v>
+        <v>3513290</v>
       </c>
       <c r="I4" t="n">
-        <v>3435087</v>
+        <v>2603430</v>
       </c>
       <c r="J4" t="n">
-        <v>956993</v>
+        <v>-3937157</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>956993</v>
+        <v>-3915922</v>
       </c>
       <c r="M4" t="n">
-        <v>7997686</v>
+        <v>3513290</v>
       </c>
       <c r="N4" t="n">
-        <v>956993</v>
+        <v>-3915922</v>
       </c>
       <c r="O4" t="n">
-        <v>956993</v>
+        <v>-3915922</v>
       </c>
       <c r="P4" t="n">
-        <v>1755000</v>
+        <v>5168376</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13863485</v>
+        <v>-4224107</v>
       </c>
       <c r="R4" t="n">
-        <v>12734731</v>
+        <v>13093064</v>
       </c>
       <c r="S4" t="n">
-        <v>91508</v>
+        <v>93007</v>
       </c>
       <c r="T4" t="n">
-        <v>91508</v>
+        <v>93007</v>
       </c>
       <c r="U4" t="n">
-        <v>8212823</v>
+        <v>8309130</v>
       </c>
       <c r="V4" t="n">
-        <v>7040693</v>
+        <v>7599017</v>
       </c>
       <c r="W4" t="n">
-        <v>2040980</v>
+        <v>169805</v>
       </c>
       <c r="X4" t="n">
-        <v>7040693</v>
+        <v>7429212</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>7040693</v>
+        <v>7429212</v>
       </c>
       <c r="AA4" t="n">
-        <v>1172130</v>
+        <v>710113</v>
       </c>
       <c r="AB4" t="n">
-        <v>383327</v>
+        <v>249908</v>
       </c>
       <c r="AC4" t="n">
-        <v>52392</v>
+        <v>428352</v>
       </c>
       <c r="AD4" t="n">
-        <v>52392</v>
+        <v>428352</v>
       </c>
       <c r="AE4" t="n">
-        <v>640170</v>
+        <v>710113</v>
       </c>
       <c r="AF4" t="n">
-        <v>390463</v>
+        <v>373814</v>
       </c>
       <c r="AG4" t="n">
-        <v>249707</v>
+        <v>336299</v>
       </c>
       <c r="AH4" t="n">
-        <v>9169816</v>
+        <v>4393208</v>
       </c>
       <c r="AI4" t="n">
-        <v>4562598</v>
+        <v>1076437</v>
       </c>
       <c r="AJ4" t="n">
-        <v>111368</v>
+        <v>100293</v>
       </c>
       <c r="AK4" t="n">
-        <v>111368</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>918218</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>918218</v>
+      </c>
       <c r="AM4" t="n">
         <v>11178</v>
       </c>
       <c r="AN4" t="n">
         <v>11178</v>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>21235</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>21235</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>33643</v>
+        <v>36691</v>
       </c>
       <c r="AR4" t="n">
-        <v>-156174</v>
+        <v>-168158</v>
       </c>
       <c r="AS4" t="n">
-        <v>189817</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+        <v>204849</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>18659</v>
+      </c>
       <c r="AU4" t="n">
-        <v>189817</v>
+        <v>186190</v>
       </c>
       <c r="AV4" t="n">
-        <v>4607217</v>
+        <v>3313543</v>
       </c>
       <c r="AW4" t="n">
         <v>-1</v>
       </c>
       <c r="AX4" t="n">
-        <v>70646</v>
+        <v>64236</v>
       </c>
       <c r="AY4" t="n">
-        <v>1602</v>
+        <v>77199</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>583384</v>
+        <v>12073</v>
       </c>
       <c r="BB4" t="n">
-        <v>562007</v>
+        <v>536749</v>
       </c>
       <c r="BC4" t="n">
-        <v>133951</v>
+        <v>176631</v>
       </c>
       <c r="BD4" t="n">
-        <v>3817634</v>
+        <v>2510891</v>
       </c>
       <c r="BE4" t="n">
-        <v>94430</v>
+        <v>918218</v>
       </c>
       <c r="BF4" t="n">
-        <v>3723204</v>
+        <v>2510891</v>
       </c>
       <c r="BG4" t="n">
-        <v>3723204</v>
+        <v>2510891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>14582</v>
+        <v>14027</v>
       </c>
       <c r="C5" t="n">
-        <v>3645723</v>
+        <v>3748478</v>
       </c>
       <c r="D5" t="n">
-        <v>3660305</v>
+        <v>3762505</v>
       </c>
       <c r="E5" t="n">
-        <v>2308445</v>
+        <v>3888907</v>
       </c>
       <c r="F5" t="n">
-        <v>5130180</v>
+        <v>4947505</v>
       </c>
       <c r="G5" t="n">
-        <v>-1565432</v>
+        <v>-4268114</v>
       </c>
       <c r="H5" t="n">
-        <v>3564748</v>
+        <v>679391</v>
       </c>
       <c r="I5" t="n">
-        <v>3294077</v>
+        <v>291838</v>
       </c>
       <c r="J5" t="n">
-        <v>-1565432</v>
-      </c>
-      <c r="K5" t="n">
+        <v>-4268114</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>-4268114</v>
+      </c>
+      <c r="M5" t="n">
+        <v>185688</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-4268114</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-4268114</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8861088</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-4264749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13311854</v>
+      </c>
+      <c r="S5" t="n">
+        <v>94063</v>
+      </c>
+      <c r="T5" t="n">
+        <v>94063</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6711786</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5018054</v>
+      </c>
+      <c r="W5" t="n">
+        <v>564252</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4453802</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>4453802</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1693732</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>493703</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>493703</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1200029</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>779877</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>420152</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2443672</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>458102</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>81508</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>350497</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>350497</v>
+      </c>
+      <c r="AM5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>-1565432</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3564748</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1565432</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1565432</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>-3413845</v>
-      </c>
-      <c r="R5" t="n">
-        <v>12734731</v>
-      </c>
-      <c r="S5" t="n">
-        <v>91508</v>
-      </c>
-      <c r="T5" t="n">
-        <v>91508</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5530440</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5130181</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5130180</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>5130180</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>400259</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20701</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>351353</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>351353</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>379558</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>200565</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>178993</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3965008</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>270672</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>123910</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>146762</v>
+        <v>26097</v>
       </c>
       <c r="AR5" t="n">
-        <v>-200379</v>
+        <v>-62286</v>
       </c>
       <c r="AS5" t="n">
-        <v>347141</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>88383</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>18660</v>
+      </c>
       <c r="AU5" t="n">
-        <v>347141</v>
+        <v>69723</v>
       </c>
       <c r="AV5" t="n">
-        <v>3694336</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
+        <v>1985570</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>58706</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>8804</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
+        <v>324965</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>12073</v>
+      </c>
       <c r="BB5" t="n">
-        <v>602567</v>
+        <v>159532</v>
       </c>
       <c r="BC5" t="n">
-        <v>107624</v>
+        <v>430402</v>
       </c>
       <c r="BD5" t="n">
-        <v>2916634</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>94899</v>
-      </c>
+        <v>1058598</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>2821735</v>
+        <v>1058598</v>
       </c>
       <c r="BG5" t="n">
-        <v>2821735</v>
+        <v>1058598</v>
       </c>
     </row>
   </sheetData>
@@ -2387,394 +2387,394 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3726876</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>-3830716</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-8633</v>
+      </c>
       <c r="D2" t="n">
-        <v>-2365670</v>
+        <v>-157767</v>
       </c>
       <c r="E2" t="n">
-        <v>3823350</v>
+        <v>2550000</v>
       </c>
       <c r="F2" t="n">
-        <v>268887</v>
+        <v>1126726</v>
       </c>
       <c r="G2" t="n">
-        <v>-5395</v>
+        <v>-3371</v>
       </c>
       <c r="H2" t="n">
-        <v>1058598</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1</v>
-      </c>
+        <v>2821735</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>2510891</v>
+        <v>3149471</v>
       </c>
       <c r="K2" t="n">
-        <v>731726</v>
+        <v>-865</v>
       </c>
       <c r="L2" t="n">
-        <v>-2184018</v>
+        <v>-326871</v>
       </c>
       <c r="M2" t="n">
-        <v>2225054</v>
+        <v>3511104</v>
       </c>
       <c r="N2" t="n">
-        <v>498487</v>
+        <v>778</v>
       </c>
       <c r="O2" t="n">
-        <v>268887</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>1118093</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-8633</v>
+      </c>
       <c r="Q2" t="n">
-        <v>268887</v>
+        <v>1126726</v>
       </c>
       <c r="R2" t="n">
-        <v>1457680</v>
+        <v>2392233</v>
       </c>
       <c r="S2" t="n">
-        <v>1457680</v>
+        <v>2392233</v>
       </c>
       <c r="T2" t="n">
-        <v>-2365670</v>
+        <v>-157767</v>
       </c>
       <c r="U2" t="n">
-        <v>3823350</v>
+        <v>2550000</v>
       </c>
       <c r="V2" t="n">
-        <v>-687591</v>
+        <v>-10630</v>
       </c>
       <c r="W2" t="n">
-        <v>-700982</v>
-      </c>
-      <c r="X2" t="n">
-        <v>18786</v>
-      </c>
+        <v>-7259</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-5395</v>
+        <v>-3371</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-5395</v>
+        <v>-3371</v>
       </c>
       <c r="AB2" t="n">
-        <v>-3721481</v>
+        <v>-3827345</v>
       </c>
       <c r="AC2" t="n">
-        <v>516269</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-442698</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-75298</v>
+        <v>29198</v>
       </c>
       <c r="AF2" t="n">
-        <v>-75298</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-16779</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>119075</v>
-      </c>
+        <v>29198</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-4264749</v>
+        <v>-3413845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4271681</v>
+        <v>-3092035</v>
       </c>
       <c r="C3" t="n">
-        <v>-12862</v>
+        <v>-12368</v>
       </c>
       <c r="D3" t="n">
-        <v>-96738</v>
+        <v>-193160</v>
       </c>
       <c r="E3" t="n">
-        <v>3598440</v>
+        <v>2405000</v>
       </c>
       <c r="F3" t="n">
-        <v>359832</v>
+        <v>1755000</v>
       </c>
       <c r="G3" t="n">
-        <v>-42433</v>
+        <v>-26992</v>
       </c>
       <c r="H3" t="n">
-        <v>2510891</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1</v>
-      </c>
+        <v>3725244</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>3725244</v>
+        <v>2821735</v>
       </c>
       <c r="K3" t="n">
-        <v>-3035</v>
+        <v>-4240</v>
       </c>
       <c r="L3" t="n">
-        <v>-1211317</v>
+        <v>907749</v>
       </c>
       <c r="M3" t="n">
-        <v>3049289</v>
+        <v>3952537</v>
       </c>
       <c r="N3" t="n">
-        <v>-799383</v>
+        <v>-1935</v>
       </c>
       <c r="O3" t="n">
-        <v>346970</v>
+        <v>1742632</v>
       </c>
       <c r="P3" t="n">
-        <v>-12862</v>
+        <v>-12368</v>
       </c>
       <c r="Q3" t="n">
-        <v>359832</v>
+        <v>1755000</v>
       </c>
       <c r="R3" t="n">
-        <v>3501702</v>
+        <v>2211840</v>
       </c>
       <c r="S3" t="n">
-        <v>3501702</v>
+        <v>2211840</v>
       </c>
       <c r="T3" t="n">
-        <v>-96738</v>
+        <v>-193160</v>
       </c>
       <c r="U3" t="n">
-        <v>3598440</v>
+        <v>2405000</v>
       </c>
       <c r="V3" t="n">
-        <v>-31358</v>
+        <v>20255</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>11075</v>
+        <v>12541</v>
       </c>
       <c r="Y3" t="n">
-        <v>-42433</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>7714</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>34706</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-42433</v>
+        <v>-26992</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4229248</v>
+        <v>-3065043</v>
       </c>
       <c r="AC3" t="n">
-        <v>-15586</v>
+        <v>467068</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>12687</v>
+        <v>31926</v>
       </c>
       <c r="AF3" t="n">
-        <v>12687</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-2242</v>
-      </c>
+        <v>31926</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-4224107</v>
+        <v>-3654592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3092035</v>
+        <v>-4271681</v>
       </c>
       <c r="C4" t="n">
-        <v>-12368</v>
+        <v>-12862</v>
       </c>
       <c r="D4" t="n">
-        <v>-193160</v>
+        <v>-96738</v>
       </c>
       <c r="E4" t="n">
-        <v>2405000</v>
+        <v>3598440</v>
       </c>
       <c r="F4" t="n">
-        <v>1755000</v>
+        <v>359832</v>
       </c>
       <c r="G4" t="n">
-        <v>-26992</v>
+        <v>-42433</v>
       </c>
       <c r="H4" t="n">
+        <v>2510891</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
         <v>3725244</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>2821735</v>
-      </c>
       <c r="K4" t="n">
-        <v>-4240</v>
+        <v>-3035</v>
       </c>
       <c r="L4" t="n">
-        <v>907749</v>
+        <v>-1211317</v>
       </c>
       <c r="M4" t="n">
-        <v>3952537</v>
+        <v>3049289</v>
       </c>
       <c r="N4" t="n">
-        <v>-1935</v>
+        <v>-799383</v>
       </c>
       <c r="O4" t="n">
-        <v>1742632</v>
+        <v>346970</v>
       </c>
       <c r="P4" t="n">
-        <v>-12368</v>
+        <v>-12862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1755000</v>
+        <v>359832</v>
       </c>
       <c r="R4" t="n">
-        <v>2211840</v>
+        <v>3501702</v>
       </c>
       <c r="S4" t="n">
-        <v>2211840</v>
+        <v>3501702</v>
       </c>
       <c r="T4" t="n">
-        <v>-193160</v>
+        <v>-96738</v>
       </c>
       <c r="U4" t="n">
-        <v>2405000</v>
+        <v>3598440</v>
       </c>
       <c r="V4" t="n">
-        <v>20255</v>
+        <v>-31358</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>12541</v>
+        <v>11075</v>
       </c>
       <c r="Y4" t="n">
-        <v>7714</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>34706</v>
-      </c>
+        <v>-42433</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-26992</v>
+        <v>-42433</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3065043</v>
+        <v>-4229248</v>
       </c>
       <c r="AC4" t="n">
-        <v>467068</v>
+        <v>-15586</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>31926</v>
+        <v>12687</v>
       </c>
       <c r="AF4" t="n">
-        <v>31926</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>12687</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-2242</v>
+      </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-3654592</v>
+        <v>-4224107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3830716</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-8633</v>
-      </c>
+        <v>-3726876</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-157767</v>
+        <v>-2365670</v>
       </c>
       <c r="E5" t="n">
-        <v>2550000</v>
+        <v>3823350</v>
       </c>
       <c r="F5" t="n">
-        <v>1126726</v>
+        <v>268887</v>
       </c>
       <c r="G5" t="n">
-        <v>-3371</v>
+        <v>-5395</v>
       </c>
       <c r="H5" t="n">
-        <v>2821735</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>1058598</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
       <c r="J5" t="n">
-        <v>3149471</v>
+        <v>2510891</v>
       </c>
       <c r="K5" t="n">
-        <v>-865</v>
+        <v>731726</v>
       </c>
       <c r="L5" t="n">
-        <v>-326871</v>
+        <v>-2184018</v>
       </c>
       <c r="M5" t="n">
-        <v>3511104</v>
+        <v>2225054</v>
       </c>
       <c r="N5" t="n">
-        <v>778</v>
+        <v>498487</v>
       </c>
       <c r="O5" t="n">
-        <v>1118093</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-8633</v>
-      </c>
+        <v>268887</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>1126726</v>
+        <v>268887</v>
       </c>
       <c r="R5" t="n">
-        <v>2392233</v>
+        <v>1457680</v>
       </c>
       <c r="S5" t="n">
-        <v>2392233</v>
+        <v>1457680</v>
       </c>
       <c r="T5" t="n">
-        <v>-157767</v>
+        <v>-2365670</v>
       </c>
       <c r="U5" t="n">
-        <v>2550000</v>
+        <v>3823350</v>
       </c>
       <c r="V5" t="n">
-        <v>-10630</v>
+        <v>-687591</v>
       </c>
       <c r="W5" t="n">
-        <v>-7259</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-700982</v>
+      </c>
+      <c r="X5" t="n">
+        <v>18786</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-3371</v>
+        <v>-5395</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-3371</v>
+        <v>-5395</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3827345</v>
+        <v>-3721481</v>
       </c>
       <c r="AC5" t="n">
-        <v>-442698</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>516269</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>29198</v>
+        <v>-75298</v>
       </c>
       <c r="AF5" t="n">
-        <v>29198</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+        <v>-75298</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-16779</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>119075</v>
+      </c>
       <c r="AI5" t="n">
-        <v>-3413845</v>
+        <v>-4264749</v>
       </c>
     </row>
   </sheetData>
@@ -3254,177 +3254,177 @@
       </c>
       <c r="CO1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="DX1" t="inlineStr">
@@ -3522,82 +3522,82 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="V2" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="X2" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.261</v>
+        <v>0.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>300</v>
+        <v>93</v>
       </c>
       <c r="AE2" t="n">
-        <v>300</v>
+        <v>93</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="AK2" t="n">
-        <v>10757571</v>
+        <v>8984344</v>
       </c>
       <c r="AL2" t="n">
-        <v>11309240</v>
+        <v>9654229</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AO2" t="n">
         <v>4.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.775361</v>
+        <v>12.339861</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.8746</v>
+        <v>2.712</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.03605</v>
+        <v>2.9885</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>14770048</v>
+        <v>13194723</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3650,16 +3650,16 @@
         <v>-1.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>20.286</v>
+        <v>18.123</v>
       </c>
       <c r="BK2" t="n">
-        <v>-4.301</v>
+        <v>-3.842</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.22625697</v>
+        <v>-0.35754192</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -3763,131 +3763,131 @@
       <c r="CO2" t="b">
         <v>0</v>
       </c>
-      <c r="CP2" t="b">
+      <c r="CP2" t="n">
+        <v>1739430000000</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>2.28 - 2.33</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>20</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.24000001</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.11764707</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>2.04 - 3.62</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>-1.3399999</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.37016574</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-35.754192</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.43199992</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.15929201</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.70850015</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.2370755</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.56971514</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_593908271</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
         <v>0</v>
       </c>
-      <c r="CQ2" t="n">
-        <v>1739430000000</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>-0.03999996</v>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>2.73 - 2.75</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DP2" t="n">
+        <v>-0.8695644</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Predilife                     A</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Predilife S.A.</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>Predilife S.A.</t>
-        </is>
-      </c>
-      <c r="CV2" t="n">
-        <v>-1.444042</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>1780429314</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>finmb_593908271</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
+      <c r="DV2" t="n">
+        <v>1782154434</v>
+      </c>
+      <c r="DW2" t="b">
         <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Predilife                     A</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>4</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.1500001</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.058139574</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>2.58 - 3.85</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>-1.1199999</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.29090908</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-22.625696</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.14459991</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.05030262</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.30605006</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.10080534</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.68215895</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
       </c>
       <c r="DX2" t="inlineStr"/>
     </row>
